--- a/inventory-budget-project.xlsx
+++ b/inventory-budget-project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jameybortnem/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F91BDC77-BCE6-234A-9CB5-CDF6F58D7D1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F177689-56B1-BB4F-9107-0524A77C75F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="28800" windowHeight="17960" xr2:uid="{8269E4BB-CF3F-4446-A6C8-67E4668EE2D7}"/>
   </bookViews>
@@ -20,6 +20,10 @@
     <sheet name="Order Overview" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">(Dashboard!$H$10:$I$10,Dashboard!$K$10:$L$10)</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">(Dashboard!$H$11:$I$11,Dashboard!$K$11:$L$11)</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">(Dashboard!$H$8:$I$8,Dashboard!$K$8:$L$8)</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">(Dashboard!$H$9:$I$9,Dashboard!$K$9:$L$9)</definedName>
     <definedName name="ExternalData_1" localSheetId="2" hidden="1">'Inventory Status'!$B$9:$G$26</definedName>
     <definedName name="ExternalData_2" localSheetId="4" hidden="1">'Order Overview'!#REF!</definedName>
     <definedName name="ExternalData_4" localSheetId="2" hidden="1">'Inventory Status'!$B$29:$G$73</definedName>
@@ -1426,7 +1430,7 @@
     <xf numFmtId="9" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="160">
+  <cellXfs count="158">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1661,15 +1665,6 @@
     <xf numFmtId="0" fontId="50" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="26" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="26" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="26" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="54" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1876,6 +1871,9 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3702,7 +3700,7 @@
             </a:r>
             <a:r>
               <a:rPr lang="en-US" sz="1800" b="1" baseline="0"/>
-              <a:t> Stock Quantity vs Total Restock Quantity</a:t>
+              <a:t> Budget vs Current Order</a:t>
             </a:r>
             <a:endParaRPr lang="en-US" sz="1800" b="1"/>
           </a:p>
@@ -3712,8 +3710,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.19025806895256767"/>
-          <c:y val="2.9131664226603057E-2"/>
+          <c:x val="0.27599427148405425"/>
+          <c:y val="2.9131791929350597E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -3758,7 +3756,7 @@
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent1">
-                <a:shade val="65000"/>
+                <a:shade val="76000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:ln>
@@ -3769,17 +3767,129 @@
           <c:invertIfNegative val="0"/>
           <c:dLbls>
             <c:dLbl>
-              <c:idx val="3"/>
+              <c:idx val="0"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1400" u="sng"/>
+                      <a:t>Total</a:t>
+                    </a:r>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1400" u="sng" baseline="0"/>
+                      <a:t> Budget </a:t>
+                    </a:r>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1400" baseline="0"/>
+                      <a:t>$6,500</a:t>
+                    </a:r>
+                    <a:endParaRPr lang="en-US" sz="1400"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
               <c:showCatName val="0"/>
-              <c:showSerName val="1"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000000-E352-2046-BF56-C830C1C5A288}"/>
+                  <c16:uniqueId val="{00000074-C5CB-774A-9FD9-9DF9637621EA}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                    <a:spAutoFit/>
+                  </a:bodyPr>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="bg1"/>
+                        </a:solidFill>
+                        <a:latin typeface="+mn-lt"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:defRPr>
+                    </a:pPr>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1400" b="1" u="sng">
+                        <a:solidFill>
+                          <a:schemeClr val="bg1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>Current</a:t>
+                    </a:r>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1400" b="1" u="sng" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="bg1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t> Order </a:t>
+                    </a:r>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1400" b="1" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="bg1"/>
+                        </a:solidFill>
+                      </a:rPr>
+                      <a:t>$6,411</a:t>
+                    </a:r>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="bg1"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000075-C5CB-774A-9FD9-9DF9637621EA}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -3797,12 +3907,9 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
+                      <a:schemeClr val="bg1"/>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -3812,52 +3919,32 @@
                 <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="ctr"/>
             <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
+            <c:showVal val="1"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
+                <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>(Dashboard!$H$8:$I$8,Dashboard!$K$8:$L$8)</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>Total Stock Quantity</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Total Restock Quantity</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>(Dashboard!$H$9:$I$9,Dashboard!$K$9:$L$9)</c:f>
+              <c:f>('Order Overview'!$G$5,'Order Overview'!$G$7)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:formatCode>"$"#,##0.00</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>6500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6411.24</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3872,163 +3959,8 @@
           <c:order val="1"/>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:dLbl>
-              <c:idx val="0"/>
-              <c:dLblPos val="outEnd"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000004-E352-2046-BF56-C830C1C5A288}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="2"/>
-              <c:dLblPos val="outEnd"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000005-E352-2046-BF56-C830C1C5A288}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="3"/>
-              <c:dLblPos val="ctr"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="1"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000001-E352-2046-BF56-C830C1C5A288}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="ctr"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>(Dashboard!$H$8:$I$8,Dashboard!$K$8:$L$8)</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>Total Stock Quantity</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Total Restock Quantity</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>(Dashboard!$H$10:$I$10,Dashboard!$K$10:$L$10)</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>406</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>160</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-0B98-6A42-8CA6-342D1814B620}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:spPr>
-            <a:solidFill>
               <a:schemeClr val="accent1">
-                <a:tint val="65000"/>
+                <a:tint val="77000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:ln>
@@ -4037,103 +3969,18 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:dLbl>
-              <c:idx val="3"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="1"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000002-E352-2046-BF56-C830C1C5A288}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>(Dashboard!$H$8:$I$8,Dashboard!$K$8:$L$8)</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>Total Stock Quantity</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Total Restock Quantity</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>(Dashboard!$H$11:$I$11,Dashboard!$K$11:$L$11)</c:f>
+              <c:f>('Order Overview'!$H$5,'Order Overview'!$H$7)</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:formatCode>"$"#,##0.00</c:formatCode>
+                <c:ptCount val="2"/>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-0B98-6A42-8CA6-342D1814B620}"/>
+              <c16:uniqueId val="{00000001-0B98-6A42-8CA6-342D1814B620}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4154,50 +4001,26 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
+        <c:delete val="1"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
         <c:crossAx val="1584853071"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
+        <c:tickLblSkip val="1"/>
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="1584853071"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="10000"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -4215,75 +4038,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1600" b="1"/>
-                  <a:t>Individual</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1600" b="1" baseline="0"/>
-                  <a:t> Items</a:t>
-                </a:r>
-                <a:endParaRPr lang="en-US" sz="1600" b="1"/>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout>
-            <c:manualLayout>
-              <c:xMode val="edge"/>
-              <c:yMode val="edge"/>
-              <c:x val="9.9693258757542549E-3"/>
-              <c:y val="0.36604280175501075"/>
-            </c:manualLayout>
-          </c:layout>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="&quot;$&quot;#,##0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -7891,12 +7646,12 @@
       <c r="Q6" s="73"/>
     </row>
     <row r="7" spans="1:17" ht="25" customHeight="1">
-      <c r="B7" s="94" t="str">
+      <c r="B7" s="91" t="str">
         <f>HYPERLINK("#'Dashboard'!A1","Inventory Overview → Dashboard ")</f>
         <v xml:space="preserve">Inventory Overview → Dashboard </v>
       </c>
-      <c r="C7" s="95"/>
-      <c r="D7" s="96"/>
+      <c r="C7" s="92"/>
+      <c r="D7" s="93"/>
       <c r="F7" s="68" t="s">
         <v>202</v>
       </c>
@@ -7913,12 +7668,12 @@
       <c r="Q7" s="70"/>
     </row>
     <row r="8" spans="1:17" ht="25" customHeight="1">
-      <c r="B8" s="91" t="str">
+      <c r="B8" s="88" t="str">
         <f>HYPERLINK("#'Inventory Status'!A1","Data Entry → Inventory Status")</f>
         <v>Data Entry → Inventory Status</v>
       </c>
-      <c r="C8" s="92"/>
-      <c r="D8" s="93"/>
+      <c r="C8" s="89"/>
+      <c r="D8" s="90"/>
       <c r="F8" s="65" t="s">
         <v>203</v>
       </c>
@@ -7935,12 +7690,12 @@
       <c r="Q8" s="67"/>
     </row>
     <row r="9" spans="1:17" ht="25" customHeight="1">
-      <c r="B9" s="91" t="str">
+      <c r="B9" s="88" t="str">
         <f>HYPERLINK("#'Expected Demand'!A1","Demand Multiplier → Expected Demand")</f>
         <v>Demand Multiplier → Expected Demand</v>
       </c>
-      <c r="C9" s="92"/>
-      <c r="D9" s="93"/>
+      <c r="C9" s="89"/>
+      <c r="D9" s="90"/>
       <c r="F9" s="65" t="s">
         <v>204</v>
       </c>
@@ -7957,12 +7712,12 @@
       <c r="Q9" s="67"/>
     </row>
     <row r="10" spans="1:17" ht="25" customHeight="1">
-      <c r="B10" s="91" t="str">
+      <c r="B10" s="88" t="str">
         <f>HYPERLINK("#'Order Overview'!A1","Order Entry → Order Overview")</f>
         <v>Order Entry → Order Overview</v>
       </c>
-      <c r="C10" s="92"/>
-      <c r="D10" s="93"/>
+      <c r="C10" s="89"/>
+      <c r="D10" s="90"/>
       <c r="F10" s="65" t="s">
         <v>205</v>
       </c>
@@ -8012,11 +7767,11 @@
     </row>
     <row r="14" spans="1:17" ht="8" customHeight="1"/>
     <row r="15" spans="1:17" ht="33" customHeight="1">
-      <c r="B15" s="71" t="s">
+      <c r="B15" s="157" t="s">
         <v>199</v>
       </c>
-      <c r="C15" s="72"/>
-      <c r="D15" s="73"/>
+      <c r="C15" s="157"/>
+      <c r="D15" s="157"/>
       <c r="F15" s="85" t="s">
         <v>208</v>
       </c>
@@ -8033,11 +7788,11 @@
       <c r="Q15" s="87"/>
     </row>
     <row r="16" spans="1:17" ht="25" customHeight="1">
-      <c r="B16" s="88">
+      <c r="B16" s="97">
         <v>46126</v>
       </c>
-      <c r="C16" s="89"/>
-      <c r="D16" s="90"/>
+      <c r="C16" s="97"/>
+      <c r="D16" s="97"/>
       <c r="F16" s="82" t="s">
         <v>209</v>
       </c>
@@ -8053,7 +7808,10 @@
       <c r="P16" s="83"/>
       <c r="Q16" s="84"/>
     </row>
-    <row r="17" spans="6:17" ht="25" customHeight="1">
+    <row r="17" spans="2:17" ht="25" customHeight="1">
+      <c r="B17" s="97"/>
+      <c r="C17" s="97"/>
+      <c r="D17" s="97"/>
       <c r="F17" s="65" t="s">
         <v>210</v>
       </c>
@@ -8069,7 +7827,7 @@
       <c r="P17" s="66"/>
       <c r="Q17" s="67"/>
     </row>
-    <row r="18" spans="6:17" ht="25" customHeight="1">
+    <row r="18" spans="2:17" ht="25" customHeight="1">
       <c r="F18" s="65" t="s">
         <v>211</v>
       </c>
@@ -8085,7 +7843,7 @@
       <c r="P18" s="66"/>
       <c r="Q18" s="67"/>
     </row>
-    <row r="19" spans="6:17" ht="25" customHeight="1">
+    <row r="19" spans="2:17" ht="25" customHeight="1">
       <c r="F19" s="65" t="s">
         <v>212</v>
       </c>
@@ -8101,7 +7859,7 @@
       <c r="P19" s="66"/>
       <c r="Q19" s="67"/>
     </row>
-    <row r="20" spans="6:17" ht="25" customHeight="1">
+    <row r="20" spans="2:17" ht="25" customHeight="1">
       <c r="F20" s="65" t="s">
         <v>213</v>
       </c>
@@ -8117,7 +7875,7 @@
       <c r="P20" s="66"/>
       <c r="Q20" s="67"/>
     </row>
-    <row r="21" spans="6:17" ht="25" customHeight="1">
+    <row r="21" spans="2:17" ht="25" customHeight="1">
       <c r="F21" s="75" t="s">
         <v>214</v>
       </c>
@@ -8138,6 +7896,7 @@
     <mergeCell ref="F12:Q12"/>
     <mergeCell ref="F11:Q11"/>
     <mergeCell ref="F10:Q10"/>
+    <mergeCell ref="B16:D17"/>
     <mergeCell ref="F21:Q21"/>
     <mergeCell ref="F20:Q20"/>
     <mergeCell ref="F19:Q19"/>
@@ -8149,7 +7908,6 @@
     <mergeCell ref="F15:Q15"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B8:D8"/>
@@ -8194,75 +7952,75 @@
   <sheetData>
     <row r="1" spans="1:18" ht="18" customHeight="1">
       <c r="A1" s="2"/>
-      <c r="B1" s="105" t="s">
+      <c r="B1" s="102" t="s">
         <v>192</v>
       </c>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-      <c r="G1" s="105"/>
-      <c r="H1" s="105"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
     </row>
     <row r="2" spans="1:18" ht="23" customHeight="1">
       <c r="A2" s="2"/>
-      <c r="B2" s="105"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="105"/>
+      <c r="B2" s="102"/>
+      <c r="C2" s="102"/>
+      <c r="D2" s="102"/>
+      <c r="E2" s="102"/>
+      <c r="F2" s="102"/>
+      <c r="G2" s="102"/>
+      <c r="H2" s="102"/>
       <c r="K2" t="s">
         <v>197</v>
       </c>
-      <c r="P2" s="99" t="s">
+      <c r="P2" s="96" t="s">
         <v>196</v>
       </c>
-      <c r="Q2" s="99"/>
-      <c r="R2" s="99"/>
+      <c r="Q2" s="96"/>
+      <c r="R2" s="96"/>
     </row>
     <row r="3" spans="1:18" ht="18" customHeight="1">
       <c r="A3" s="2"/>
-      <c r="B3" s="105"/>
-      <c r="C3" s="105"/>
-      <c r="D3" s="105"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="105"/>
-      <c r="G3" s="105"/>
-      <c r="H3" s="105"/>
-      <c r="P3" s="99"/>
-      <c r="Q3" s="99"/>
-      <c r="R3" s="99"/>
+      <c r="B3" s="102"/>
+      <c r="C3" s="102"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="102"/>
+      <c r="P3" s="96"/>
+      <c r="Q3" s="96"/>
+      <c r="R3" s="96"/>
     </row>
     <row r="4" spans="1:18" ht="18" customHeight="1">
       <c r="A4" s="2"/>
       <c r="B4" s="42"/>
       <c r="C4" s="43"/>
       <c r="D4" s="43"/>
-      <c r="P4" s="100">
-        <f>'Inventory Status'!G3</f>
-        <v>46091</v>
-      </c>
-      <c r="Q4" s="100"/>
-      <c r="R4" s="100"/>
+      <c r="P4" s="97">
+        <f>Introduction!B16</f>
+        <v>46126</v>
+      </c>
+      <c r="Q4" s="97"/>
+      <c r="R4" s="97"/>
     </row>
     <row r="5" spans="1:18" ht="23" customHeight="1">
       <c r="A5" s="2"/>
-      <c r="B5" s="97" t="s">
+      <c r="B5" s="94" t="s">
         <v>218</v>
       </c>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
-      <c r="E5" s="97"/>
-      <c r="F5" s="97"/>
+      <c r="C5" s="94"/>
+      <c r="D5" s="94"/>
+      <c r="E5" s="94"/>
+      <c r="F5" s="94"/>
       <c r="G5" s="44"/>
       <c r="H5" s="44"/>
       <c r="I5" s="44"/>
       <c r="J5" s="44"/>
-      <c r="P5" s="100"/>
-      <c r="Q5" s="100"/>
-      <c r="R5" s="100"/>
+      <c r="P5" s="97"/>
+      <c r="Q5" s="97"/>
+      <c r="R5" s="97"/>
     </row>
     <row r="6" spans="1:18" ht="8" customHeight="1">
       <c r="A6" s="2"/>
@@ -8286,12 +8044,12 @@
     </row>
     <row r="7" spans="1:18" ht="18" customHeight="1">
       <c r="A7" s="2"/>
-      <c r="B7" s="98" t="s">
+      <c r="B7" s="95" t="s">
         <v>216</v>
       </c>
-      <c r="C7" s="98"/>
-      <c r="D7" s="98"/>
-      <c r="E7" s="98"/>
+      <c r="C7" s="95"/>
+      <c r="D7" s="95"/>
+      <c r="E7" s="95"/>
       <c r="F7" s="48"/>
       <c r="G7" s="44"/>
       <c r="H7" s="44"/>
@@ -8307,110 +8065,110 @@
       <c r="R7" s="44"/>
     </row>
     <row r="8" spans="1:18" ht="23" customHeight="1">
-      <c r="B8" s="99" t="s">
+      <c r="B8" s="96" t="s">
         <v>217</v>
       </c>
-      <c r="C8" s="99"/>
+      <c r="C8" s="96"/>
       <c r="D8" s="49"/>
-      <c r="E8" s="99" t="s">
+      <c r="E8" s="96" t="s">
         <v>191</v>
       </c>
-      <c r="F8" s="99"/>
+      <c r="F8" s="96"/>
       <c r="G8" s="49"/>
-      <c r="H8" s="99" t="s">
+      <c r="H8" s="96" t="s">
         <v>189</v>
       </c>
-      <c r="I8" s="99"/>
+      <c r="I8" s="96"/>
       <c r="J8" s="50"/>
-      <c r="K8" s="99" t="s">
+      <c r="K8" s="96" t="s">
         <v>193</v>
       </c>
-      <c r="L8" s="99"/>
+      <c r="L8" s="96"/>
       <c r="M8" s="50"/>
-      <c r="N8" s="106" t="s">
+      <c r="N8" s="103" t="s">
         <v>195</v>
       </c>
-      <c r="O8" s="107"/>
+      <c r="O8" s="104"/>
       <c r="P8" s="50"/>
-      <c r="Q8" s="106" t="s">
+      <c r="Q8" s="103" t="s">
         <v>194</v>
       </c>
-      <c r="R8" s="107"/>
+      <c r="R8" s="104"/>
     </row>
     <row r="9" spans="1:18" ht="23" customHeight="1">
-      <c r="B9" s="99"/>
-      <c r="C9" s="99"/>
+      <c r="B9" s="96"/>
+      <c r="C9" s="96"/>
       <c r="D9" s="49"/>
-      <c r="E9" s="99"/>
-      <c r="F9" s="99"/>
+      <c r="E9" s="96"/>
+      <c r="F9" s="96"/>
       <c r="G9" s="49"/>
-      <c r="H9" s="99"/>
-      <c r="I9" s="99"/>
+      <c r="H9" s="96"/>
+      <c r="I9" s="96"/>
       <c r="J9" s="50"/>
-      <c r="K9" s="99"/>
-      <c r="L9" s="99"/>
+      <c r="K9" s="96"/>
+      <c r="L9" s="96"/>
       <c r="M9" s="50"/>
-      <c r="N9" s="108"/>
-      <c r="O9" s="109"/>
+      <c r="N9" s="105"/>
+      <c r="O9" s="106"/>
       <c r="P9" s="50"/>
-      <c r="Q9" s="108"/>
-      <c r="R9" s="109"/>
+      <c r="Q9" s="105"/>
+      <c r="R9" s="106"/>
     </row>
     <row r="10" spans="1:18" ht="23" customHeight="1">
-      <c r="B10" s="110">
+      <c r="B10" s="107">
         <f>COUNTA('Inventory Status'!B10:B26,'Inventory Status'!B30:B73,'Inventory Status'!B77:B158)</f>
         <v>134</v>
       </c>
-      <c r="C10" s="111"/>
+      <c r="C10" s="108"/>
       <c r="D10" s="20"/>
-      <c r="E10" s="114">
+      <c r="E10" s="111">
         <f>SUM('Inventory Status'!F10:F26,'Inventory Status'!F30:F73,'Inventory Status'!F77:F158)</f>
         <v>454.75</v>
       </c>
-      <c r="F10" s="115"/>
+      <c r="F10" s="112"/>
       <c r="G10" s="20"/>
-      <c r="H10" s="110">
+      <c r="H10" s="107">
         <f>SUM('Inventory Status'!E10:E26,'Inventory Status'!E30:E73,'Inventory Status'!E77:E158)</f>
         <v>406</v>
       </c>
-      <c r="I10" s="111"/>
+      <c r="I10" s="108"/>
       <c r="J10" s="20"/>
-      <c r="K10" s="110">
+      <c r="K10" s="107">
         <f>SUM(SUMIF('Inventory Status'!G10:G26,"&gt;0"),SUMIF('Inventory Status'!G30:G73,"&gt;0"), SUMIF('Inventory Status'!G77:G158,"&gt;0"))</f>
-        <v>160</v>
-      </c>
-      <c r="L10" s="111"/>
+        <v>159</v>
+      </c>
+      <c r="L10" s="108"/>
       <c r="M10" s="20"/>
-      <c r="N10" s="101">
+      <c r="N10" s="98">
         <f>COUNTIF('Inventory Status'!B10:H158,"YES") / (COUNTIF('Inventory Status'!B10:H158,"YES") + (COUNTIF('Inventory Status'!B10:H158,"NO")))</f>
         <v>0.43283582089552236</v>
       </c>
-      <c r="O10" s="102"/>
+      <c r="O10" s="99"/>
       <c r="P10" s="20"/>
-      <c r="Q10" s="101">
+      <c r="Q10" s="98">
         <f>COUNTIF('Inventory Status'!B10:H158,"NO") / (COUNTIF('Inventory Status'!B10:H158,"YES") + (COUNTIF('Inventory Status'!B10:H158,"NO")))</f>
         <v>0.56716417910447758</v>
       </c>
-      <c r="R10" s="102"/>
+      <c r="R10" s="99"/>
     </row>
     <row r="11" spans="1:18" ht="23" customHeight="1">
-      <c r="B11" s="112"/>
-      <c r="C11" s="113"/>
+      <c r="B11" s="109"/>
+      <c r="C11" s="110"/>
       <c r="D11" s="20"/>
-      <c r="E11" s="116"/>
-      <c r="F11" s="117"/>
+      <c r="E11" s="113"/>
+      <c r="F11" s="114"/>
       <c r="G11" s="20"/>
-      <c r="H11" s="112"/>
-      <c r="I11" s="113"/>
+      <c r="H11" s="109"/>
+      <c r="I11" s="110"/>
       <c r="J11" s="20"/>
-      <c r="K11" s="112"/>
-      <c r="L11" s="113"/>
+      <c r="K11" s="109"/>
+      <c r="L11" s="110"/>
       <c r="M11" s="20"/>
-      <c r="N11" s="103"/>
-      <c r="O11" s="104"/>
+      <c r="N11" s="100"/>
+      <c r="O11" s="101"/>
       <c r="P11" s="20"/>
-      <c r="Q11" s="103"/>
-      <c r="R11" s="104"/>
+      <c r="Q11" s="100"/>
+      <c r="R11" s="101"/>
     </row>
     <row r="12" spans="1:18" ht="14" customHeight="1"/>
     <row r="13" spans="1:18"/>
@@ -8490,37 +8248,38 @@
   <sheetData>
     <row r="1" spans="1:18" ht="18" customHeight="1">
       <c r="A1" s="2"/>
-      <c r="B1" s="120" t="s">
+      <c r="B1" s="117" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="120"/>
+      <c r="C1" s="117"/>
       <c r="F1" s="3"/>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1">
       <c r="A2" s="2"/>
-      <c r="B2" s="120"/>
-      <c r="C2" s="120"/>
+      <c r="B2" s="117"/>
+      <c r="C2" s="117"/>
     </row>
     <row r="3" spans="1:18" ht="18" customHeight="1">
       <c r="A3" s="2"/>
-      <c r="B3" s="120"/>
-      <c r="C3" s="120"/>
-      <c r="E3" s="119" t="s">
+      <c r="B3" s="117"/>
+      <c r="C3" s="117"/>
+      <c r="E3" s="116" t="s">
         <v>200</v>
       </c>
-      <c r="F3" s="119"/>
-      <c r="G3" s="121">
-        <v>46091</v>
-      </c>
-      <c r="H3" s="122"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="118">
+        <f>Introduction!B16</f>
+        <v>46126</v>
+      </c>
+      <c r="H3" s="119"/>
     </row>
     <row r="4" spans="1:18" ht="18" customHeight="1">
       <c r="A4" s="2"/>
       <c r="C4" s="4"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="123"/>
-      <c r="H4" s="124"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="121"/>
     </row>
     <row r="5" spans="1:18" ht="23" customHeight="1">
       <c r="A5" s="2"/>
@@ -8528,10 +8287,10 @@
         <v>218</v>
       </c>
       <c r="C5" s="9"/>
-      <c r="E5" s="119"/>
-      <c r="F5" s="119"/>
-      <c r="G5" s="125"/>
-      <c r="H5" s="126"/>
+      <c r="E5" s="116"/>
+      <c r="F5" s="116"/>
+      <c r="G5" s="122"/>
+      <c r="H5" s="123"/>
     </row>
     <row r="6" spans="1:18" ht="18" customHeight="1">
       <c r="A6" s="2"/>
@@ -8551,15 +8310,15 @@
       <c r="F7" s="10"/>
     </row>
     <row r="8" spans="1:18" ht="34" customHeight="1">
-      <c r="B8" s="118" t="s">
+      <c r="B8" s="115" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="118"/>
-      <c r="D8" s="118"/>
-      <c r="E8" s="118"/>
-      <c r="F8" s="118"/>
-      <c r="G8" s="118"/>
-      <c r="H8" s="118"/>
+      <c r="C8" s="115"/>
+      <c r="D8" s="115"/>
+      <c r="E8" s="115"/>
+      <c r="F8" s="115"/>
+      <c r="G8" s="115"/>
+      <c r="H8" s="115"/>
     </row>
     <row r="9" spans="1:18" ht="19" customHeight="1">
       <c r="B9" s="56" t="s">
@@ -8606,7 +8365,7 @@
         <v>12</v>
       </c>
       <c r="G10" s="8">
-        <f>frozeninventory[[#This Row],[Target Quantity]]-frozeninventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,frozeninventory[[#This Row],[Target Quantity]]-frozeninventory[[#This Row],[Current Quantity]])</f>
         <v>9</v>
       </c>
       <c r="H10" s="8" t="str">
@@ -8631,7 +8390,7 @@
         <v>8</v>
       </c>
       <c r="G11" s="8">
-        <f>frozeninventory[[#This Row],[Target Quantity]]-frozeninventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,frozeninventory[[#This Row],[Target Quantity]]-frozeninventory[[#This Row],[Current Quantity]])</f>
         <v>1</v>
       </c>
       <c r="H11" s="8" t="str">
@@ -8656,7 +8415,7 @@
         <v>2</v>
       </c>
       <c r="G12" s="8">
-        <f>frozeninventory[[#This Row],[Target Quantity]]-frozeninventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,frozeninventory[[#This Row],[Target Quantity]]-frozeninventory[[#This Row],[Current Quantity]])</f>
         <v>1</v>
       </c>
       <c r="H12" s="8" t="str">
@@ -8681,7 +8440,7 @@
         <v>3</v>
       </c>
       <c r="G13" s="8">
-        <f>frozeninventory[[#This Row],[Target Quantity]]-frozeninventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,frozeninventory[[#This Row],[Target Quantity]]-frozeninventory[[#This Row],[Current Quantity]])</f>
         <v>0</v>
       </c>
       <c r="H13" s="8" t="str">
@@ -8706,8 +8465,8 @@
         <v>10</v>
       </c>
       <c r="G14" s="8">
-        <f>frozeninventory[[#This Row],[Target Quantity]]-frozeninventory[[#This Row],[Current Quantity]]</f>
-        <v>-2</v>
+        <f>MAX(0,frozeninventory[[#This Row],[Target Quantity]]-frozeninventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H14" s="8" t="str">
         <f>IF(frozeninventory[[#This Row],[Needed Quantity]]&gt;0, "YES","NO")</f>
@@ -8731,7 +8490,7 @@
         <v>5</v>
       </c>
       <c r="G15" s="8">
-        <f>frozeninventory[[#This Row],[Target Quantity]]-frozeninventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,frozeninventory[[#This Row],[Target Quantity]]-frozeninventory[[#This Row],[Current Quantity]])</f>
         <v>4</v>
       </c>
       <c r="H15" s="8" t="str">
@@ -8756,7 +8515,7 @@
         <v>3</v>
       </c>
       <c r="G16" s="8">
-        <f>frozeninventory[[#This Row],[Target Quantity]]-frozeninventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,frozeninventory[[#This Row],[Target Quantity]]-frozeninventory[[#This Row],[Current Quantity]])</f>
         <v>2</v>
       </c>
       <c r="H16" s="8" t="str">
@@ -8781,7 +8540,7 @@
         <v>3</v>
       </c>
       <c r="G17" s="8">
-        <f>frozeninventory[[#This Row],[Target Quantity]]-frozeninventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,frozeninventory[[#This Row],[Target Quantity]]-frozeninventory[[#This Row],[Current Quantity]])</f>
         <v>1</v>
       </c>
       <c r="H17" s="8" t="str">
@@ -8806,7 +8565,7 @@
         <v>8</v>
       </c>
       <c r="G18" s="8">
-        <f>frozeninventory[[#This Row],[Target Quantity]]-frozeninventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,frozeninventory[[#This Row],[Target Quantity]]-frozeninventory[[#This Row],[Current Quantity]])</f>
         <v>8</v>
       </c>
       <c r="H18" s="8" t="str">
@@ -8831,7 +8590,7 @@
         <v>2</v>
       </c>
       <c r="G19" s="8">
-        <f>frozeninventory[[#This Row],[Target Quantity]]-frozeninventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,frozeninventory[[#This Row],[Target Quantity]]-frozeninventory[[#This Row],[Current Quantity]])</f>
         <v>2</v>
       </c>
       <c r="H19" s="8" t="str">
@@ -8856,8 +8615,8 @@
         <v>6</v>
       </c>
       <c r="G20" s="8">
-        <f>frozeninventory[[#This Row],[Target Quantity]]-frozeninventory[[#This Row],[Current Quantity]]</f>
-        <v>-2</v>
+        <f>MAX(0,frozeninventory[[#This Row],[Target Quantity]]-frozeninventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H20" s="8" t="str">
         <f>IF(frozeninventory[[#This Row],[Needed Quantity]]&gt;0, "YES","NO")</f>
@@ -8881,7 +8640,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="8">
-        <f>frozeninventory[[#This Row],[Target Quantity]]-frozeninventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,frozeninventory[[#This Row],[Target Quantity]]-frozeninventory[[#This Row],[Current Quantity]])</f>
         <v>0</v>
       </c>
       <c r="H21" s="8" t="str">
@@ -8906,8 +8665,8 @@
         <v>3</v>
       </c>
       <c r="G22" s="8">
-        <f>frozeninventory[[#This Row],[Target Quantity]]-frozeninventory[[#This Row],[Current Quantity]]</f>
-        <v>-5</v>
+        <f>MAX(0,frozeninventory[[#This Row],[Target Quantity]]-frozeninventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H22" s="8" t="str">
         <f>IF(frozeninventory[[#This Row],[Needed Quantity]]&gt;0, "YES","NO")</f>
@@ -8958,15 +8717,15 @@
       <c r="G27" s="6"/>
     </row>
     <row r="28" spans="2:8" ht="34" customHeight="1">
-      <c r="B28" s="118" t="s">
+      <c r="B28" s="115" t="s">
         <v>13</v>
       </c>
-      <c r="C28" s="118"/>
-      <c r="D28" s="118"/>
-      <c r="E28" s="118"/>
-      <c r="F28" s="118"/>
-      <c r="G28" s="118"/>
-      <c r="H28" s="118"/>
+      <c r="C28" s="115"/>
+      <c r="D28" s="115"/>
+      <c r="E28" s="115"/>
+      <c r="F28" s="115"/>
+      <c r="G28" s="115"/>
+      <c r="H28" s="115"/>
     </row>
     <row r="29" spans="2:8" ht="18" customHeight="1">
       <c r="B29" s="56" t="s">
@@ -9008,8 +8767,8 @@
         <v>10</v>
       </c>
       <c r="G30" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
-        <v>-10</v>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H30" s="8" t="str">
         <f>IF(refridgeratedinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -9033,8 +8792,8 @@
         <v>10</v>
       </c>
       <c r="G31" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
-        <v>-5</v>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H31" s="8" t="str">
         <f>IF(refridgeratedinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -9058,7 +8817,7 @@
         <v>1</v>
       </c>
       <c r="G32" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
         <v>1</v>
       </c>
       <c r="H32" s="8" t="str">
@@ -9083,7 +8842,7 @@
         <v>4</v>
       </c>
       <c r="G33" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
         <v>2</v>
       </c>
       <c r="H33" s="8" t="str">
@@ -9108,7 +8867,7 @@
         <v>8</v>
       </c>
       <c r="G34" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
         <v>4</v>
       </c>
       <c r="H34" s="8" t="str">
@@ -9133,7 +8892,7 @@
         <v>3</v>
       </c>
       <c r="G35" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
         <v>1</v>
       </c>
       <c r="H35" s="8" t="str">
@@ -9158,7 +8917,7 @@
         <v>3</v>
       </c>
       <c r="G36" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
         <v>2</v>
       </c>
       <c r="H36" s="8" t="str">
@@ -9183,7 +8942,7 @@
         <v>6</v>
       </c>
       <c r="G37" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
         <v>5</v>
       </c>
       <c r="H37" s="8" t="str">
@@ -9208,7 +8967,7 @@
         <v>3</v>
       </c>
       <c r="G38" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
         <v>0</v>
       </c>
       <c r="H38" s="8" t="str">
@@ -9233,7 +8992,7 @@
         <v>3</v>
       </c>
       <c r="G39" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
         <v>2</v>
       </c>
       <c r="H39" s="8" t="str">
@@ -9258,7 +9017,7 @@
         <v>3</v>
       </c>
       <c r="G40" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
         <v>0</v>
       </c>
       <c r="H40" s="8" t="str">
@@ -9283,7 +9042,7 @@
         <v>12</v>
       </c>
       <c r="G41" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
         <v>1</v>
       </c>
       <c r="H41" s="8" t="str">
@@ -9308,8 +9067,8 @@
         <v>15</v>
       </c>
       <c r="G42" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
-        <v>-2</v>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H42" s="8" t="str">
         <f>IF(refridgeratedinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -9333,8 +9092,8 @@
         <v>10</v>
       </c>
       <c r="G43" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
-        <v>-3</v>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H43" s="8" t="str">
         <f>IF(refridgeratedinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -9358,8 +9117,8 @@
         <v>10</v>
       </c>
       <c r="G44" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
-        <v>-2</v>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H44" s="8" t="str">
         <f>IF(refridgeratedinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -9383,7 +9142,7 @@
         <v>10</v>
       </c>
       <c r="G45" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
         <v>2</v>
       </c>
       <c r="H45" s="8" t="str">
@@ -9408,7 +9167,7 @@
         <v>10</v>
       </c>
       <c r="G46" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
         <v>8</v>
       </c>
       <c r="H46" s="8" t="str">
@@ -9433,7 +9192,7 @@
         <v>8</v>
       </c>
       <c r="G47" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
         <v>8</v>
       </c>
       <c r="H47" s="8" t="str">
@@ -9458,8 +9217,8 @@
         <v>0.5</v>
       </c>
       <c r="G48" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
-        <v>-0.5</v>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H48" s="8" t="str">
         <f>IF(refridgeratedinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -9483,8 +9242,8 @@
         <v>0.5</v>
       </c>
       <c r="G49" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
-        <v>-0.5</v>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H49" s="8" t="str">
         <f>IF(refridgeratedinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -9508,8 +9267,8 @@
         <v>0.5</v>
       </c>
       <c r="G50" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
-        <v>-0.5</v>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H50" s="8" t="str">
         <f>IF(refridgeratedinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -9533,7 +9292,7 @@
         <v>1</v>
       </c>
       <c r="G51" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
         <v>0</v>
       </c>
       <c r="H51" s="8" t="str">
@@ -9558,7 +9317,7 @@
         <v>12</v>
       </c>
       <c r="G52" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
         <v>10</v>
       </c>
       <c r="H52" s="8" t="str">
@@ -9583,7 +9342,7 @@
         <v>3</v>
       </c>
       <c r="G53" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
         <v>2</v>
       </c>
       <c r="H53" s="8" t="str">
@@ -9608,7 +9367,7 @@
         <v>2</v>
       </c>
       <c r="G54" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
         <v>1</v>
       </c>
       <c r="H54" s="8" t="str">
@@ -9633,7 +9392,7 @@
         <v>1</v>
       </c>
       <c r="G55" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
         <v>0</v>
       </c>
       <c r="H55" s="8" t="str">
@@ -9658,7 +9417,7 @@
         <v>3</v>
       </c>
       <c r="G56" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
         <v>1</v>
       </c>
       <c r="H56" s="8" t="str">
@@ -9683,7 +9442,7 @@
         <v>3</v>
       </c>
       <c r="G57" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
         <v>1</v>
       </c>
       <c r="H57" s="8" t="str">
@@ -9708,7 +9467,7 @@
         <v>2</v>
       </c>
       <c r="G58" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
         <v>1</v>
       </c>
       <c r="H58" s="8" t="str">
@@ -9733,7 +9492,7 @@
         <v>1</v>
       </c>
       <c r="G59" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
         <v>0</v>
       </c>
       <c r="H59" s="8" t="str">
@@ -9758,7 +9517,7 @@
         <v>1</v>
       </c>
       <c r="G60" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
         <v>0</v>
       </c>
       <c r="H60" s="8" t="str">
@@ -9783,8 +9542,8 @@
         <v>1</v>
       </c>
       <c r="G61" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
-        <v>-1</v>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H61" s="8" t="str">
         <f>IF(refridgeratedinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -9808,7 +9567,7 @@
         <v>1</v>
       </c>
       <c r="G62" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
         <v>0</v>
       </c>
       <c r="H62" s="8" t="str">
@@ -9833,7 +9592,7 @@
         <v>1</v>
       </c>
       <c r="G63" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
         <v>1</v>
       </c>
       <c r="H63" s="8" t="str">
@@ -9858,7 +9617,7 @@
         <v>1</v>
       </c>
       <c r="G64" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
         <v>1</v>
       </c>
       <c r="H64" s="8" t="str">
@@ -9883,7 +9642,7 @@
         <v>2</v>
       </c>
       <c r="G65" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
         <v>1</v>
       </c>
       <c r="H65" s="8" t="str">
@@ -9908,7 +9667,7 @@
         <v>1</v>
       </c>
       <c r="G66" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
         <v>1</v>
       </c>
       <c r="H66" s="8" t="str">
@@ -9933,7 +9692,7 @@
         <v>1</v>
       </c>
       <c r="G67" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
         <v>0</v>
       </c>
       <c r="H67" s="8" t="str">
@@ -9958,8 +9717,8 @@
         <v>1</v>
       </c>
       <c r="G68" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
-        <v>-2</v>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H68" s="8" t="str">
         <f>IF(refridgeratedinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -9983,7 +9742,7 @@
         <v>5</v>
       </c>
       <c r="G69" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
         <v>1</v>
       </c>
       <c r="H69" s="8" t="str">
@@ -10008,8 +9767,8 @@
         <v>2</v>
       </c>
       <c r="G70" s="8">
-        <f>refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]]</f>
-        <v>-2</v>
+        <f>MAX(0,refridgeratedinventory[[#This Row],[Target Quantity]]-refridgeratedinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H70" s="8" t="str">
         <f>IF(refridgeratedinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -10045,15 +9804,15 @@
     </row>
     <row r="74" spans="2:8" ht="19" customHeight="1"/>
     <row r="75" spans="2:8" ht="34" customHeight="1">
-      <c r="B75" s="118" t="s">
+      <c r="B75" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="C75" s="118"/>
-      <c r="D75" s="118"/>
-      <c r="E75" s="118"/>
-      <c r="F75" s="118"/>
-      <c r="G75" s="118"/>
-      <c r="H75" s="118"/>
+      <c r="C75" s="115"/>
+      <c r="D75" s="115"/>
+      <c r="E75" s="115"/>
+      <c r="F75" s="115"/>
+      <c r="G75" s="115"/>
+      <c r="H75" s="115"/>
     </row>
     <row r="76" spans="2:8" ht="19" customHeight="1">
       <c r="B76" s="56" t="s">
@@ -10095,8 +9854,8 @@
         <v>10</v>
       </c>
       <c r="G77" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-5</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H77" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -10120,8 +9879,8 @@
         <v>1</v>
       </c>
       <c r="G78" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-2</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H78" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -10145,8 +9904,8 @@
         <v>1</v>
       </c>
       <c r="G79" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-2</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H79" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -10170,7 +9929,7 @@
         <v>2</v>
       </c>
       <c r="G80" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>0</v>
       </c>
       <c r="H80" s="8" t="str">
@@ -10195,7 +9954,7 @@
         <v>1</v>
       </c>
       <c r="G81" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>1</v>
       </c>
       <c r="H81" s="8" t="str">
@@ -10220,8 +9979,8 @@
         <v>1</v>
       </c>
       <c r="G82" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-2</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H82" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -10245,8 +10004,8 @@
         <v>1</v>
       </c>
       <c r="G83" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-3</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H83" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -10270,7 +10029,7 @@
         <v>2</v>
       </c>
       <c r="G84" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>1</v>
       </c>
       <c r="H84" s="8" t="str">
@@ -10295,7 +10054,7 @@
         <v>3</v>
       </c>
       <c r="G85" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>2</v>
       </c>
       <c r="H85" s="8" t="str">
@@ -10320,8 +10079,8 @@
         <v>3</v>
       </c>
       <c r="G86" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-2</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H86" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -10345,8 +10104,8 @@
         <v>3</v>
       </c>
       <c r="G87" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-3</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H87" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -10370,7 +10129,7 @@
         <v>15</v>
       </c>
       <c r="G88" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>2</v>
       </c>
       <c r="H88" s="8" t="str">
@@ -10395,7 +10154,7 @@
         <v>15</v>
       </c>
       <c r="G89" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>3</v>
       </c>
       <c r="H89" s="8" t="str">
@@ -10420,8 +10179,8 @@
         <v>0.5</v>
       </c>
       <c r="G90" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-0.5</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H90" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -10445,7 +10204,7 @@
         <v>15</v>
       </c>
       <c r="G91" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>11</v>
       </c>
       <c r="H91" s="8" t="str">
@@ -10470,7 +10229,7 @@
         <v>1</v>
       </c>
       <c r="G92" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>0</v>
       </c>
       <c r="H92" s="8" t="str">
@@ -10495,8 +10254,8 @@
         <v>0.5</v>
       </c>
       <c r="G93" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-0.5</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H93" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -10520,7 +10279,7 @@
         <v>0.5</v>
       </c>
       <c r="G94" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>0.5</v>
       </c>
       <c r="H94" s="8" t="str">
@@ -10545,7 +10304,7 @@
         <v>2</v>
       </c>
       <c r="G95" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>0</v>
       </c>
       <c r="H95" s="8" t="str">
@@ -10570,8 +10329,8 @@
         <v>3</v>
       </c>
       <c r="G96" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-1</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H96" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -10595,8 +10354,8 @@
         <v>0.5</v>
       </c>
       <c r="G97" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-0.5</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H97" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -10620,8 +10379,8 @@
         <v>0.25</v>
       </c>
       <c r="G98" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-0.75</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H98" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -10645,7 +10404,7 @@
         <v>1</v>
       </c>
       <c r="G99" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>0</v>
       </c>
       <c r="H99" s="8" t="str">
@@ -10670,7 +10429,7 @@
         <v>1</v>
       </c>
       <c r="G100" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>0</v>
       </c>
       <c r="H100" s="8" t="str">
@@ -10695,8 +10454,8 @@
         <v>0.5</v>
       </c>
       <c r="G101" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-2.5</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H101" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -10720,7 +10479,7 @@
         <v>1</v>
       </c>
       <c r="G102" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>1</v>
       </c>
       <c r="H102" s="8" t="str">
@@ -10745,7 +10504,7 @@
         <v>2</v>
       </c>
       <c r="G103" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>1</v>
       </c>
       <c r="H103" s="8" t="str">
@@ -10770,7 +10529,7 @@
         <v>2</v>
       </c>
       <c r="G104" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>1</v>
       </c>
       <c r="H104" s="8" t="str">
@@ -10795,8 +10554,8 @@
         <v>10</v>
       </c>
       <c r="G105" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-2</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H105" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -10820,7 +10579,7 @@
         <v>5</v>
       </c>
       <c r="G106" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>0</v>
       </c>
       <c r="H106" s="8" t="str">
@@ -10845,7 +10604,7 @@
         <v>2</v>
       </c>
       <c r="G107" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>0</v>
       </c>
       <c r="H107" s="8" t="str">
@@ -10870,7 +10629,7 @@
         <v>8</v>
       </c>
       <c r="G108" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>5</v>
       </c>
       <c r="H108" s="8" t="str">
@@ -10895,7 +10654,7 @@
         <v>1</v>
       </c>
       <c r="G109" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>0</v>
       </c>
       <c r="H109" s="8" t="str">
@@ -10920,7 +10679,7 @@
         <v>5</v>
       </c>
       <c r="G110" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>3</v>
       </c>
       <c r="H110" s="8" t="str">
@@ -10945,7 +10704,7 @@
         <v>6</v>
       </c>
       <c r="G111" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>1</v>
       </c>
       <c r="H111" s="8" t="str">
@@ -10970,8 +10729,8 @@
         <v>2</v>
       </c>
       <c r="G112" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-2</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H112" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -10995,8 +10754,8 @@
         <v>3</v>
       </c>
       <c r="G113" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-2</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H113" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -11020,7 +10779,7 @@
         <v>1</v>
       </c>
       <c r="G114" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>0</v>
       </c>
       <c r="H114" s="8" t="str">
@@ -11045,7 +10804,7 @@
         <v>3</v>
       </c>
       <c r="G115" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>2</v>
       </c>
       <c r="H115" s="8" t="str">
@@ -11070,8 +10829,8 @@
         <v>1</v>
       </c>
       <c r="G116" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-1</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H116" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -11095,7 +10854,7 @@
         <v>1</v>
       </c>
       <c r="G117" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>0</v>
       </c>
       <c r="H117" s="8" t="str">
@@ -11120,8 +10879,8 @@
         <v>1</v>
       </c>
       <c r="G118" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-3</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H118" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -11145,8 +10904,8 @@
         <v>1</v>
       </c>
       <c r="G119" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-4</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H119" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -11170,7 +10929,7 @@
         <v>3</v>
       </c>
       <c r="G120" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>1</v>
       </c>
       <c r="H120" s="8" t="str">
@@ -11195,7 +10954,7 @@
         <v>2</v>
       </c>
       <c r="G121" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>2</v>
       </c>
       <c r="H121" s="8" t="str">
@@ -11220,7 +10979,7 @@
         <v>1</v>
       </c>
       <c r="G122" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>0</v>
       </c>
       <c r="H122" s="8" t="str">
@@ -11245,8 +11004,8 @@
         <v>1</v>
       </c>
       <c r="G123" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-1</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H123" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -11270,8 +11029,8 @@
         <v>1</v>
       </c>
       <c r="G124" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-2</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H124" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -11295,7 +11054,7 @@
         <v>1</v>
       </c>
       <c r="G125" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>0</v>
       </c>
       <c r="H125" s="8" t="str">
@@ -11320,8 +11079,8 @@
         <v>1</v>
       </c>
       <c r="G126" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-4</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H126" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -11345,7 +11104,7 @@
         <v>1</v>
       </c>
       <c r="G127" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>0</v>
       </c>
       <c r="H127" s="8" t="str">
@@ -11370,7 +11129,7 @@
         <v>1</v>
       </c>
       <c r="G128" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>1</v>
       </c>
       <c r="H128" s="8" t="str">
@@ -11395,8 +11154,8 @@
         <v>0.5</v>
       </c>
       <c r="G129" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-0.5</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H129" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -11420,7 +11179,7 @@
         <v>1</v>
       </c>
       <c r="G130" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>0</v>
       </c>
       <c r="H130" s="8" t="str">
@@ -11445,8 +11204,8 @@
         <v>0.5</v>
       </c>
       <c r="G131" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-4.5</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H131" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -11470,8 +11229,8 @@
         <v>0.5</v>
       </c>
       <c r="G132" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-1.5</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H132" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -11495,7 +11254,7 @@
         <v>0.5</v>
       </c>
       <c r="G133" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>0.5</v>
       </c>
       <c r="H133" s="8" t="str">
@@ -11520,8 +11279,8 @@
         <v>0.5</v>
       </c>
       <c r="G134" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-0.5</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H134" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -11545,8 +11304,8 @@
         <v>0.5</v>
       </c>
       <c r="G135" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-1.5</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H135" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -11570,8 +11329,8 @@
         <v>1</v>
       </c>
       <c r="G136" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-2</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H136" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -11595,8 +11354,8 @@
         <v>0.5</v>
       </c>
       <c r="G137" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-0.5</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H137" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -11620,8 +11379,8 @@
         <v>2</v>
       </c>
       <c r="G138" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-3</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H138" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -11645,7 +11404,7 @@
         <v>6</v>
       </c>
       <c r="G139" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>5</v>
       </c>
       <c r="H139" s="8" t="str">
@@ -11670,8 +11429,8 @@
         <v>3</v>
       </c>
       <c r="G140" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-2</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H140" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -11695,8 +11454,8 @@
         <v>1</v>
       </c>
       <c r="G141" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-1</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H141" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -11720,7 +11479,7 @@
         <v>1</v>
       </c>
       <c r="G142" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>1</v>
       </c>
       <c r="H142" s="8" t="str">
@@ -11745,7 +11504,7 @@
         <v>3</v>
       </c>
       <c r="G143" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>2</v>
       </c>
       <c r="H143" s="8" t="str">
@@ -11770,8 +11529,8 @@
         <v>0.5</v>
       </c>
       <c r="G144" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-1.5</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H144" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -11795,8 +11554,8 @@
         <v>0.5</v>
       </c>
       <c r="G145" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-2.5</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H145" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -11820,8 +11579,8 @@
         <v>0.5</v>
       </c>
       <c r="G146" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-0.5</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H146" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -11845,8 +11604,8 @@
         <v>3</v>
       </c>
       <c r="G147" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-2</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H147" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -11870,7 +11629,7 @@
         <v>5</v>
       </c>
       <c r="G148" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>4</v>
       </c>
       <c r="H148" s="8" t="str">
@@ -11895,7 +11654,7 @@
         <v>2</v>
       </c>
       <c r="G149" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>2</v>
       </c>
       <c r="H149" s="8" t="str">
@@ -11920,7 +11679,7 @@
         <v>2</v>
       </c>
       <c r="G150" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>1</v>
       </c>
       <c r="H150" s="8" t="str">
@@ -11945,7 +11704,7 @@
         <v>15</v>
       </c>
       <c r="G151" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>14</v>
       </c>
       <c r="H151" s="8" t="str">
@@ -11970,7 +11729,7 @@
         <v>3</v>
       </c>
       <c r="G152" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>3</v>
       </c>
       <c r="H152" s="8" t="str">
@@ -11995,8 +11754,8 @@
         <v>0.5</v>
       </c>
       <c r="G153" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-2.5</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H153" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -12020,8 +11779,8 @@
         <v>3</v>
       </c>
       <c r="G154" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
-        <v>-1</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>0</v>
       </c>
       <c r="H154" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -12045,7 +11804,7 @@
         <v>3</v>
       </c>
       <c r="G155" s="8">
-        <f>dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]]</f>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
         <v>1</v>
       </c>
       <c r="H155" s="8" t="str">
@@ -12070,7 +11829,8 @@
         <v>3</v>
       </c>
       <c r="G156" s="8">
-        <v>3</v>
+        <f>MAX(0,dryinventory[[#This Row],[Target Quantity]]-dryinventory[[#This Row],[Current Quantity]])</f>
+        <v>2</v>
       </c>
       <c r="H156" s="8" t="str">
         <f>IF(dryinventory[[#This Row],[Quantity Needed]]&gt;0, "YES","NO")</f>
@@ -12166,22 +11926,22 @@
   <sheetData>
     <row r="1" spans="1:18" ht="18" customHeight="1">
       <c r="A1" s="2"/>
-      <c r="B1" s="128" t="s">
+      <c r="B1" s="125" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="128"/>
+      <c r="C1" s="125"/>
       <c r="F1" s="3"/>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1">
       <c r="A2" s="2"/>
-      <c r="B2" s="128"/>
-      <c r="C2" s="128"/>
+      <c r="B2" s="125"/>
+      <c r="C2" s="125"/>
       <c r="F2" s="11"/>
     </row>
     <row r="3" spans="1:18" ht="18" customHeight="1">
       <c r="A3" s="2"/>
-      <c r="B3" s="128"/>
-      <c r="C3" s="128"/>
+      <c r="B3" s="125"/>
+      <c r="C3" s="125"/>
       <c r="F3" s="11"/>
     </row>
     <row r="4" spans="1:18" ht="18" customHeight="1">
@@ -12213,18 +11973,19 @@
       <c r="F7" s="10"/>
     </row>
     <row r="8" spans="1:18" ht="20" customHeight="1">
-      <c r="B8" s="133" t="s">
+      <c r="B8" s="130" t="s">
         <v>199</v>
       </c>
-      <c r="C8" s="134">
-        <v>46091</v>
+      <c r="C8" s="131">
+        <f>Introduction!B16</f>
+        <v>46126</v>
       </c>
       <c r="D8" s="15"/>
       <c r="G8" s="15"/>
     </row>
     <row r="9" spans="1:18" ht="20" customHeight="1">
-      <c r="B9" s="133"/>
-      <c r="C9" s="134"/>
+      <c r="B9" s="130"/>
+      <c r="C9" s="131"/>
       <c r="D9" s="12"/>
       <c r="G9" s="12"/>
       <c r="N9" s="5"/>
@@ -12234,8 +11995,8 @@
       <c r="R9" s="5"/>
     </row>
     <row r="10" spans="1:18" ht="18" customHeight="1">
-      <c r="B10" s="133"/>
-      <c r="C10" s="134"/>
+      <c r="B10" s="130"/>
+      <c r="C10" s="131"/>
       <c r="D10" s="14"/>
       <c r="G10" s="14"/>
     </row>
@@ -12252,24 +12013,24 @@
       <c r="G12" s="14"/>
     </row>
     <row r="13" spans="1:18" ht="18" customHeight="1">
-      <c r="B13" s="135" t="s">
+      <c r="B13" s="132" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="136" t="s">
+      <c r="C13" s="133" t="s">
         <v>125</v>
       </c>
       <c r="D13" s="14"/>
       <c r="G13" s="14"/>
     </row>
     <row r="14" spans="1:18" ht="18" customHeight="1">
-      <c r="B14" s="135"/>
-      <c r="C14" s="137"/>
+      <c r="B14" s="132"/>
+      <c r="C14" s="134"/>
       <c r="D14" s="14"/>
       <c r="G14" s="14"/>
     </row>
     <row r="15" spans="1:18" ht="18" customHeight="1">
-      <c r="B15" s="135"/>
-      <c r="C15" s="138"/>
+      <c r="B15" s="132"/>
+      <c r="C15" s="135"/>
       <c r="D15" s="14"/>
       <c r="G15" s="14"/>
     </row>
@@ -12284,18 +12045,18 @@
       <c r="G17" s="14"/>
     </row>
     <row r="18" spans="2:7" ht="18" customHeight="1">
-      <c r="B18" s="129" t="s">
+      <c r="B18" s="126" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="130"/>
+      <c r="C18" s="127"/>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="14"/>
       <c r="G18" s="14"/>
     </row>
     <row r="19" spans="2:7" ht="18" customHeight="1">
-      <c r="B19" s="131"/>
-      <c r="C19" s="132"/>
+      <c r="B19" s="128"/>
+      <c r="C19" s="129"/>
       <c r="D19" s="14"/>
       <c r="E19" s="14"/>
       <c r="F19" s="14"/>
@@ -12414,12 +12175,12 @@
       <c r="G31" s="13"/>
     </row>
     <row r="32" spans="2:7" ht="26" hidden="1" customHeight="1">
-      <c r="B32" s="127"/>
-      <c r="C32" s="127"/>
-      <c r="D32" s="127"/>
-      <c r="E32" s="127"/>
-      <c r="F32" s="127"/>
-      <c r="G32" s="127"/>
+      <c r="B32" s="124"/>
+      <c r="C32" s="124"/>
+      <c r="D32" s="124"/>
+      <c r="E32" s="124"/>
+      <c r="F32" s="124"/>
+      <c r="G32" s="124"/>
     </row>
     <row r="33" spans="2:7" ht="18" hidden="1" customHeight="1">
       <c r="B33" s="12"/>
@@ -12606,12 +12367,12 @@
       <c r="G55" s="13"/>
     </row>
     <row r="56" spans="2:7" ht="26" hidden="1" customHeight="1">
-      <c r="B56" s="127"/>
-      <c r="C56" s="127"/>
-      <c r="D56" s="127"/>
-      <c r="E56" s="127"/>
-      <c r="F56" s="127"/>
-      <c r="G56" s="127"/>
+      <c r="B56" s="124"/>
+      <c r="C56" s="124"/>
+      <c r="D56" s="124"/>
+      <c r="E56" s="124"/>
+      <c r="F56" s="124"/>
+      <c r="G56" s="124"/>
     </row>
     <row r="57" spans="2:7" ht="18" hidden="1" customHeight="1">
       <c r="B57" s="12"/>
@@ -12859,33 +12620,34 @@
   <sheetData>
     <row r="1" spans="1:18" ht="18" customHeight="1">
       <c r="A1" s="2"/>
-      <c r="B1" s="139" t="s">
+      <c r="B1" s="136" t="s">
         <v>135</v>
       </c>
-      <c r="C1" s="139"/>
+      <c r="C1" s="136"/>
       <c r="F1" s="3"/>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1">
       <c r="A2" s="2"/>
-      <c r="B2" s="139"/>
-      <c r="C2" s="139"/>
-      <c r="E2" s="151" t="s">
+      <c r="B2" s="136"/>
+      <c r="C2" s="136"/>
+      <c r="E2" s="148" t="s">
         <v>199</v>
       </c>
-      <c r="F2" s="151"/>
-      <c r="G2" s="152">
-        <v>46091</v>
-      </c>
-      <c r="H2" s="153"/>
+      <c r="F2" s="148"/>
+      <c r="G2" s="149">
+        <f>Introduction!B16</f>
+        <v>46126</v>
+      </c>
+      <c r="H2" s="150"/>
     </row>
     <row r="3" spans="1:18" ht="18" customHeight="1">
       <c r="A3" s="2"/>
-      <c r="B3" s="139"/>
-      <c r="C3" s="139"/>
-      <c r="E3" s="151"/>
-      <c r="F3" s="151"/>
-      <c r="G3" s="154"/>
-      <c r="H3" s="155"/>
+      <c r="B3" s="136"/>
+      <c r="C3" s="136"/>
+      <c r="E3" s="148"/>
+      <c r="F3" s="148"/>
+      <c r="G3" s="151"/>
+      <c r="H3" s="152"/>
     </row>
     <row r="4" spans="1:18" ht="18" customHeight="1">
       <c r="A4" s="2"/>
@@ -12897,35 +12659,35 @@
     </row>
     <row r="5" spans="1:18" ht="35" customHeight="1">
       <c r="A5" s="2"/>
-      <c r="B5" s="150"/>
-      <c r="C5" s="150"/>
-      <c r="E5" s="156" t="s">
+      <c r="B5" s="147"/>
+      <c r="C5" s="147"/>
+      <c r="E5" s="153" t="s">
         <v>182</v>
       </c>
-      <c r="F5" s="156"/>
-      <c r="G5" s="149">
+      <c r="F5" s="153"/>
+      <c r="G5" s="146">
         <v>6500</v>
       </c>
-      <c r="H5" s="149"/>
+      <c r="H5" s="146"/>
     </row>
     <row r="6" spans="1:18" ht="19" customHeight="1">
       <c r="A6" s="2"/>
     </row>
     <row r="7" spans="1:18" ht="35" customHeight="1">
       <c r="A7" s="2"/>
-      <c r="B7" s="159" t="s">
+      <c r="B7" s="156" t="s">
         <v>218</v>
       </c>
-      <c r="C7" s="159"/>
-      <c r="E7" s="156" t="s">
+      <c r="C7" s="156"/>
+      <c r="E7" s="153" t="s">
         <v>181</v>
       </c>
-      <c r="F7" s="156"/>
-      <c r="G7" s="157">
+      <c r="F7" s="153"/>
+      <c r="G7" s="154">
         <f>SUM(H28,H77,H164)</f>
         <v>6411.24</v>
       </c>
-      <c r="H7" s="157"/>
+      <c r="H7" s="154"/>
     </row>
     <row r="8" spans="1:18" ht="18" customHeight="1">
       <c r="B8" s="51" t="s">
@@ -12934,15 +12696,15 @@
       <c r="C8" s="1"/>
     </row>
     <row r="9" spans="1:18" ht="34" customHeight="1">
-      <c r="B9" s="143" t="s">
+      <c r="B9" s="140" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="144"/>
-      <c r="D9" s="144"/>
-      <c r="E9" s="144"/>
-      <c r="F9" s="144"/>
-      <c r="G9" s="144"/>
-      <c r="H9" s="145"/>
+      <c r="C9" s="141"/>
+      <c r="D9" s="141"/>
+      <c r="E9" s="141"/>
+      <c r="F9" s="141"/>
+      <c r="G9" s="141"/>
+      <c r="H9" s="142"/>
     </row>
     <row r="10" spans="1:18" ht="19" customHeight="1">
       <c r="B10" s="25" t="s">
@@ -13099,7 +12861,7 @@
       </c>
       <c r="E15" s="29">
         <f>IF('Inventory Status'!G14="","",'Inventory Status'!G14)*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])</f>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="F15" s="36">
         <v>46.82</v>
@@ -13267,7 +13029,7 @@
       </c>
       <c r="E21" s="29">
         <f>IF('Inventory Status'!G20="","",'Inventory Status'!G20)*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])</f>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="F21" s="36">
         <v>23.45</v>
@@ -13323,7 +13085,7 @@
       </c>
       <c r="E23" s="29">
         <f>IF('Inventory Status'!G22="","",'Inventory Status'!G22)*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])</f>
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="F23" s="36">
         <v>108.4</v>
@@ -13422,30 +13184,30 @@
     </row>
     <row r="28" spans="2:8" ht="16" customHeight="1">
       <c r="F28" s="30"/>
-      <c r="G28" s="148" t="s">
+      <c r="G28" s="145" t="s">
         <v>177</v>
       </c>
-      <c r="H28" s="146">
+      <c r="H28" s="143">
         <f>SUM(frozenorder[Line Price])</f>
         <v>1702.96</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="16" customHeight="1">
       <c r="F29" s="30"/>
-      <c r="G29" s="148"/>
-      <c r="H29" s="147"/>
+      <c r="G29" s="145"/>
+      <c r="H29" s="144"/>
     </row>
     <row r="30" spans="2:8"/>
     <row r="31" spans="2:8" ht="29">
-      <c r="B31" s="140" t="s">
+      <c r="B31" s="137" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="141"/>
-      <c r="D31" s="141"/>
-      <c r="E31" s="141"/>
-      <c r="F31" s="141"/>
-      <c r="G31" s="141"/>
-      <c r="H31" s="142"/>
+      <c r="C31" s="138"/>
+      <c r="D31" s="138"/>
+      <c r="E31" s="138"/>
+      <c r="F31" s="138"/>
+      <c r="G31" s="138"/>
+      <c r="H31" s="139"/>
     </row>
     <row r="32" spans="2:8">
       <c r="B32" s="25" t="s">
@@ -13485,7 +13247,7 @@
       </c>
       <c r="E33" s="29">
         <f>IF('Inventory Status'!G30*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G30*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="F33" s="39">
         <v>32.340000000000003</v>
@@ -13513,7 +13275,7 @@
       </c>
       <c r="E34" s="29">
         <f>IF('Inventory Status'!G31*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G31*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="F34" s="32">
         <v>22.45</v>
@@ -13821,7 +13583,7 @@
       </c>
       <c r="E45" s="29">
         <f>IF('Inventory Status'!G42*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G42*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="F45" s="32">
         <v>29.08</v>
@@ -13849,7 +13611,7 @@
       </c>
       <c r="E46" s="29">
         <f>IF('Inventory Status'!G43*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G43*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F46" s="32">
         <v>29.87</v>
@@ -13877,7 +13639,7 @@
       </c>
       <c r="E47" s="29">
         <f>IF('Inventory Status'!G44*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G44*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="F47" s="32">
         <v>29.87</v>
@@ -13989,7 +13751,7 @@
       </c>
       <c r="E51" s="29">
         <f>IF('Inventory Status'!G48*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G48*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="F51" s="32">
         <v>45.61</v>
@@ -14017,7 +13779,7 @@
       </c>
       <c r="E52" s="29">
         <f>IF('Inventory Status'!G49*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G49*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="F52" s="32">
         <v>29.61</v>
@@ -14045,7 +13807,7 @@
       </c>
       <c r="E53" s="29">
         <f>IF('Inventory Status'!G50*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G50*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="F53" s="32">
         <v>16.78</v>
@@ -14353,7 +14115,7 @@
       </c>
       <c r="E64" s="29">
         <f>IF('Inventory Status'!G61*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G61*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F64" s="32">
         <v>34.56</v>
@@ -14549,7 +14311,7 @@
       </c>
       <c r="E71" s="29">
         <f>IF('Inventory Status'!G68*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G68*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="F71" s="32">
         <v>38.46</v>
@@ -14605,7 +14367,7 @@
       </c>
       <c r="E73" s="29">
         <f>IF('Inventory Status'!G70*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G70*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="F73" s="32">
         <v>83.34</v>
@@ -14682,32 +14444,32 @@
       </c>
     </row>
     <row r="77" spans="2:8" ht="20" customHeight="1">
-      <c r="G77" s="158" t="s">
+      <c r="G77" s="155" t="s">
         <v>179</v>
       </c>
-      <c r="H77" s="146">
+      <c r="H77" s="143">
         <f>SUM(refridgeratedorder[Line Price])</f>
         <v>2106.88</v>
       </c>
     </row>
     <row r="78" spans="2:8" ht="16" customHeight="1">
-      <c r="G78" s="158"/>
-      <c r="H78" s="146"/>
+      <c r="G78" s="155"/>
+      <c r="H78" s="143"/>
     </row>
     <row r="79" spans="2:8" ht="20" customHeight="1">
       <c r="G79" s="33"/>
       <c r="H79" s="34"/>
     </row>
     <row r="80" spans="2:8" ht="29">
-      <c r="B80" s="156" t="s">
+      <c r="B80" s="153" t="s">
         <v>12</v>
       </c>
-      <c r="C80" s="156"/>
-      <c r="D80" s="156"/>
-      <c r="E80" s="156"/>
-      <c r="F80" s="156"/>
-      <c r="G80" s="156"/>
-      <c r="H80" s="156"/>
+      <c r="C80" s="153"/>
+      <c r="D80" s="153"/>
+      <c r="E80" s="153"/>
+      <c r="F80" s="153"/>
+      <c r="G80" s="153"/>
+      <c r="H80" s="153"/>
     </row>
     <row r="81" spans="2:8">
       <c r="B81" s="27" t="s">
@@ -14747,7 +14509,7 @@
       </c>
       <c r="E82" s="8">
         <f>IF('Inventory Status'!G77*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G77*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="F82" s="32">
         <v>32.909999999999997</v>
@@ -14775,7 +14537,7 @@
       </c>
       <c r="E83" s="8">
         <f>IF('Inventory Status'!G78*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G78*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="F83" s="32">
         <v>31.45</v>
@@ -14803,7 +14565,7 @@
       </c>
       <c r="E84" s="8">
         <f>IF('Inventory Status'!G79*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G79*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="F84" s="32">
         <v>31.54</v>
@@ -14887,7 +14649,7 @@
       </c>
       <c r="E87" s="8">
         <f>IF('Inventory Status'!G82*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G82*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="F87" s="32">
         <v>22.31</v>
@@ -14915,7 +14677,7 @@
       </c>
       <c r="E88" s="8">
         <f>IF('Inventory Status'!G83*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G83*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F88" s="32">
         <v>42.87</v>
@@ -14999,7 +14761,7 @@
       </c>
       <c r="E91" s="8">
         <f>IF('Inventory Status'!G86*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G86*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="F91" s="32">
         <v>32.15</v>
@@ -15027,7 +14789,7 @@
       </c>
       <c r="E92" s="8">
         <f>IF('Inventory Status'!G87*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G87*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F92" s="32">
         <v>53.51</v>
@@ -15111,7 +14873,7 @@
       </c>
       <c r="E95" s="8">
         <f>IF('Inventory Status'!G90*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G90*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="F95" s="32">
         <v>31.41</v>
@@ -15195,7 +14957,7 @@
       </c>
       <c r="E98" s="8">
         <f>IF('Inventory Status'!G93*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G93*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="F98" s="32">
         <v>46.8</v>
@@ -15279,7 +15041,7 @@
       </c>
       <c r="E101" s="8">
         <f>IF('Inventory Status'!G96*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G96*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F101" s="32">
         <v>49.36</v>
@@ -15307,7 +15069,7 @@
       </c>
       <c r="E102" s="8">
         <f>IF('Inventory Status'!G97*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G97*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="F102" s="32">
         <v>44.41</v>
@@ -15335,7 +15097,7 @@
       </c>
       <c r="E103" s="8">
         <f>IF('Inventory Status'!G98*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G98*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-0.75</v>
+        <v>0</v>
       </c>
       <c r="F103" s="32">
         <v>18.7</v>
@@ -15419,7 +15181,7 @@
       </c>
       <c r="E106" s="8">
         <f>IF('Inventory Status'!G101*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G101*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="F106" s="32">
         <v>45.21</v>
@@ -15531,7 +15293,7 @@
       </c>
       <c r="E110" s="8">
         <f>IF('Inventory Status'!G105*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G105*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="F110" s="32">
         <v>100.38</v>
@@ -15727,7 +15489,7 @@
       </c>
       <c r="E117" s="8">
         <f>IF('Inventory Status'!G112*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G112*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="F117" s="32">
         <v>29.08</v>
@@ -15755,7 +15517,7 @@
       </c>
       <c r="E118" s="8">
         <f>IF('Inventory Status'!G113*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G113*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="F118" s="32">
         <v>29.87</v>
@@ -15839,7 +15601,7 @@
       </c>
       <c r="E121" s="8">
         <f>IF('Inventory Status'!G116*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G116*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F121" s="32">
         <v>20.100000000000001</v>
@@ -15895,7 +15657,7 @@
       </c>
       <c r="E123" s="8">
         <f>IF('Inventory Status'!G118*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G118*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F123" s="32">
         <v>55.32</v>
@@ -15923,7 +15685,7 @@
       </c>
       <c r="E124" s="8">
         <f>IF('Inventory Status'!G119*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G119*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="F124" s="32">
         <v>28.09</v>
@@ -16035,7 +15797,7 @@
       </c>
       <c r="E128" s="8">
         <f>IF('Inventory Status'!G123*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G123*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F128" s="32">
         <v>39.83</v>
@@ -16063,7 +15825,7 @@
       </c>
       <c r="E129" s="8">
         <f>IF('Inventory Status'!G124*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G124*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="F129" s="32">
         <v>29.06</v>
@@ -16119,7 +15881,7 @@
       </c>
       <c r="E131" s="8">
         <f>IF('Inventory Status'!G126*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G126*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="F131" s="32">
         <v>22.69</v>
@@ -16203,7 +15965,7 @@
       </c>
       <c r="E134" s="8">
         <f>IF('Inventory Status'!G129*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G129*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="F134" s="32">
         <v>48.82</v>
@@ -16259,7 +16021,7 @@
       </c>
       <c r="E136" s="8">
         <f>IF('Inventory Status'!G131*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G131*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-4.5</v>
+        <v>0</v>
       </c>
       <c r="F136" s="32">
         <v>31.54</v>
@@ -16287,7 +16049,7 @@
       </c>
       <c r="E137" s="8">
         <f>IF('Inventory Status'!G132*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G132*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="F137" s="32">
         <v>23.7</v>
@@ -16343,7 +16105,7 @@
       </c>
       <c r="E139" s="8">
         <f>IF('Inventory Status'!G134*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G134*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="F139" s="32">
         <v>22.31</v>
@@ -16371,7 +16133,7 @@
       </c>
       <c r="E140" s="8">
         <f>IF('Inventory Status'!G135*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G135*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="F140" s="32">
         <v>42.87</v>
@@ -16399,7 +16161,7 @@
       </c>
       <c r="E141" s="8">
         <f>IF('Inventory Status'!G136*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G136*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="F141" s="32">
         <v>30.73</v>
@@ -16427,7 +16189,7 @@
       </c>
       <c r="E142" s="8">
         <f>IF('Inventory Status'!G137*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G137*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="F142" s="32">
         <v>31.21</v>
@@ -16455,7 +16217,7 @@
       </c>
       <c r="E143" s="8">
         <f>IF('Inventory Status'!G138*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G138*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F143" s="32">
         <v>32.15</v>
@@ -16511,7 +16273,7 @@
       </c>
       <c r="E145" s="8">
         <f>IF('Inventory Status'!G140*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G140*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="F145" s="32">
         <v>55.62</v>
@@ -16539,7 +16301,7 @@
       </c>
       <c r="E146" s="8">
         <f>IF('Inventory Status'!G141*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G141*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F146" s="32">
         <v>53.92</v>
@@ -16623,7 +16385,7 @@
       </c>
       <c r="E149" s="8">
         <f>IF('Inventory Status'!G144*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G144*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="F149" s="32">
         <v>29.08</v>
@@ -16651,7 +16413,7 @@
       </c>
       <c r="E150" s="8">
         <f>IF('Inventory Status'!G145*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G145*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="F150" s="32">
         <v>29.87</v>
@@ -16679,7 +16441,7 @@
       </c>
       <c r="E151" s="8">
         <f>IF('Inventory Status'!G146*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G146*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="F151" s="32">
         <v>31.41</v>
@@ -16707,7 +16469,7 @@
       </c>
       <c r="E152" s="8">
         <f>IF('Inventory Status'!G147*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G147*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="F152" s="32">
         <v>38.340000000000003</v>
@@ -16875,7 +16637,7 @@
       </c>
       <c r="E158" s="8">
         <f>IF('Inventory Status'!G153*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G153*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="F158" s="32">
         <v>31.53</v>
@@ -16903,7 +16665,7 @@
       </c>
       <c r="E159" s="8">
         <f>IF('Inventory Status'!G154*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G154*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F159" s="32">
         <v>22.89</v>
@@ -16959,7 +16721,7 @@
       </c>
       <c r="E161" s="8">
         <f>IF('Inventory Status'!G156*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier])="","",'Inventory Status'!G156*_xlfn.XLOOKUP('Expected Demand'!$C$13,Table33[Demand Level],Table33[Multiplier]))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F161" s="32">
         <v>36.21</v>
@@ -17015,17 +16777,17 @@
       </c>
     </row>
     <row r="164" spans="2:8">
-      <c r="G164" s="148" t="s">
+      <c r="G164" s="145" t="s">
         <v>180</v>
       </c>
-      <c r="H164" s="146">
+      <c r="H164" s="143">
         <f>SUM(dryorder[Line Price])</f>
         <v>2601.3999999999992</v>
       </c>
     </row>
     <row r="165" spans="2:8">
-      <c r="G165" s="148"/>
-      <c r="H165" s="146"/>
+      <c r="G165" s="145"/>
+      <c r="H165" s="143"/>
     </row>
     <row r="166" spans="2:8"/>
     <row r="167" spans="2:8"/>
